--- a/stories/arbres/ATOM-LAN.NOM.001-06.xlsx
+++ b/stories/arbres/ATOM-LAN.NOM.001-06.xlsx
@@ -481,7 +481,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B29"/>
+  <dimension ref="A1:B30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -602,7 +602,6 @@
           <t>secondary_lessons</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -819,6 +818,18 @@
       <c r="B29" t="inlineStr">
         <is>
           <t>xlsx-arbre-v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>voice_cast</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>voix-roles-v1</t>
         </is>
       </c>
     </row>
@@ -833,7 +844,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AV6"/>
+  <dimension ref="A1:AW6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1127,6 +1138,11 @@
           <t>notes</t>
         </is>
       </c>
+      <c r="AW1" t="inlineStr">
+        <is>
+          <t>script</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1151,7 +1167,7 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Aurore est à la cuisine avec maman. Des cuillères sont sur la table. Maman dit : on compte des objets. Aurore touche. Un. Deux. Trois. Quatre. Cinq. Elle dit : cinq cuillères. Maman en pose encore. Six. Sept. Huit. Neuf. Dix. Aurore répète : dix. Elle a compté des objets. Elle a dit le nombre.</t>
+          <t>Aurore est à la cuisine avec maman. Des cuillères sont sur la table. On compte des objets. Aurore touche. Un. Deux. Trois. Quatre. Cinq. Cinq cuillères. Maman en pose encore. Six. Sept. Huit. Neuf. Dix. Aurore répète : dix. Elle a compté des objets. Elle a dit le nombre.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -1285,6 +1301,15 @@
         <v>8</v>
       </c>
       <c r="AV2" s="2" t="inlineStr"/>
+      <c r="AW2" t="inlineStr">
+        <is>
+          <t>narrateur|Aurore est à la cuisine avec maman. Des cuillères sont sur la table.
+maman|On compte des objets.
+narrateur|Aurore touche. Un. Deux. Trois. Quatre. Cinq.
+narrateur|Cinq cuillères. Maman en pose encore. Six. Sept. Huit. Neuf. Dix.
+narrateur|Aurore répète : dix. Elle a compté des objets. Elle a dit le nombre.</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1461,6 +1486,11 @@
       <c r="AV3" s="2" t="inlineStr">
         <is>
           <t>question d'écoute, ne change pas le cours</t>
+        </is>
+      </c>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>narrateur|Aurore touche les cuillères. Que fait-elle ?</t>
         </is>
       </c>
     </row>
@@ -1625,6 +1655,11 @@
           <t>confirmation ; le moteur peut dire engine_ok/near avant ce chunk</t>
         </is>
       </c>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>narrateur|Aurore a compté des objets. Elle a dit le nombre.</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1783,6 +1818,11 @@
         <v>8</v>
       </c>
       <c r="AV5" s="2" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>narrateur|Maman range les cuillères. Aurore essuie la table.</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -1945,6 +1985,11 @@
         <v>8</v>
       </c>
       <c r="AV6" s="2" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -1963,7 +2008,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A2"/>
+  <dimension ref="A1:A3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -1980,6 +2025,13 @@
       <c r="A2" t="inlineStr">
         <is>
           <t>conversion structurelle, prompts de choix alignés, TTS profilé</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-LAN.NOM.001-06.xlsx
+++ b/stories/arbres/ATOM-LAN.NOM.001-06.xlsx
@@ -844,7 +844,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW6"/>
+  <dimension ref="A1:AX6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1143,6 +1143,11 @@
           <t>script</t>
         </is>
       </c>
+      <c r="AX1" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1310,6 +1315,7 @@
 narrateur|Aurore répète : dix. Elle a compté des objets. Elle a dit le nombre.</t>
         </is>
       </c>
+      <c r="AX2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1493,6 +1499,7 @@
           <t>narrateur|Aurore touche les cuillères. Que fait-elle ?</t>
         </is>
       </c>
+      <c r="AX3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1660,6 +1667,7 @@
           <t>narrateur|Aurore a compté des objets. Elle a dit le nombre.</t>
         </is>
       </c>
+      <c r="AX4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1823,6 +1831,7 @@
           <t>narrateur|Maman range les cuillères. Aurore essuie la table.</t>
         </is>
       </c>
+      <c r="AX5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -1990,6 +1999,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX6" t="inlineStr"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -2008,7 +2018,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A3"/>
+  <dimension ref="A1:A5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2032,6 +2042,20 @@
       <c r="A3" t="inlineStr">
         <is>
           <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
         </is>
       </c>
     </row>
@@ -2046,7 +2070,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B15"/>
+  <dimension ref="A1:B16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -2233,6 +2257,18 @@
         </is>
       </c>
     </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>ids de bruits (vide = silence). Le bruit se joue, puis l'histoire reprend au calme.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/stories/arbres/ATOM-LAN.NOM.001-06.xlsx
+++ b/stories/arbres/ATOM-LAN.NOM.001-06.xlsx
@@ -481,7 +481,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B30"/>
+  <dimension ref="A1:B31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -544,7 +544,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Aurore compte les cuillères</t>
+          <t>Nina compte les cuillères</t>
         </is>
       </c>
     </row>
@@ -830,6 +830,18 @@
       <c r="B30" t="inlineStr">
         <is>
           <t>voix-roles-v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>fil_rouge</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Le tiroir grince. Nina touche les cuillères de bois. Elle compte jusqu'à dix. Papa et maman disent le nombre.</t>
         </is>
       </c>
     </row>
@@ -1172,7 +1184,7 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Aurore est à la cuisine avec maman. Des cuillères sont sur la table. On compte des objets. Aurore touche. Un. Deux. Trois. Quatre. Cinq. Cinq cuillères. Maman en pose encore. Six. Sept. Huit. Neuf. Dix. Aurore répète : dix. Elle a compté des objets. Elle a dit le nombre.</t>
+          <t>Le tiroir grince, puis s'ouvre. Le bois sent le chaud de la pièce. Une cuillère en bois dépasse. Le manche est lisse et un peu taché. La casserole chuchote sur le feu doux. Ça sent la soupe de carottes. Un napperon beige attend sur la table. Il a un petit trou au coin. La fenêtre laisse un carré de lumière. Nina, tu as entendu le tiroir ? Oui, papa. Ça grince. Les cuillères sont là. Ça sent la soupe. En ce moment, Nina s'approche de la table. Des cuillères sont alignées. Elles sont en bois, un peu mates. On compte des objets. On touche. On dit le nombre. Nina touche une cuillère. Une. Elle en touche une autre. Deux. Trois. Quatre. Cinq. Cinq cuillères. Tu as dit le nombre. Maman en pose encore. Le bois tape tout doux. Six. Sept. Huit. Neuf. Dix. Dix. Tu as compté des objets. Dix cuillères. Bravo, Nina. Tu as fait du bon travail. Nina aligne les cuillères. Les manches se touchent. Les objets sont là. On peut dire le nombre. La soupe chuchote encore. Le napperon reste beige. Le bois est lisse, hein ? Oui. Lisse. On range le tiroir ? Oui, papa. Nina pose les cuillères une à une. Le tiroir se ferme tout doux. Papa pose des bols sur le napperon. Les bols sont blancs et chauds. On compte aussi les bols. Nina touche un bol. Un. Deux. Trois. Quatre. Cinq. Cinq bols. Tu dis le nombre. Cinq. Tu as compté des objets. La vapeur sent encore la carotte. Le carré de lumière a bougé. Cuillères, puis bols. J'ai dit le nombre. Le tiroir reste fermé. Nina pose sa main sur le bois. Le bois est tiède.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -1308,14 +1320,76 @@
       <c r="AV2" s="2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>narrateur|Aurore est à la cuisine avec maman. Des cuillères sont sur la table.
+          <t>narrateur|Le tiroir grince, puis s'ouvre.
+narrateur|Le bois sent le chaud de la pièce.
+narrateur|Une cuillère en bois dépasse.
+narrateur|Le manche est lisse et un peu taché.
+narrateur|La casserole chuchote sur le feu doux.
+narrateur|Ça sent la soupe de carottes.
+narrateur|Un napperon beige attend sur la table.
+narrateur|Il a un petit trou au coin.
+narrateur|La fenêtre laisse un carré de lumière.
+papa|Nina, tu as entendu le tiroir ?
+enfant-f|Oui, papa.
+enfant-f|Ça grince.
+maman|Les cuillères sont là.
+papa|Ça sent la soupe.
+narrateur|En ce moment, Nina s'approche de la table.
+narrateur|Des cuillères sont alignées.
+narrateur|Elles sont en bois, un peu mates.
 maman|On compte des objets.
-narrateur|Aurore touche. Un. Deux. Trois. Quatre. Cinq.
-narrateur|Cinq cuillères. Maman en pose encore. Six. Sept. Huit. Neuf. Dix.
-narrateur|Aurore répète : dix. Elle a compté des objets. Elle a dit le nombre.</t>
-        </is>
-      </c>
-      <c r="AX2" t="inlineStr"/>
+papa|On touche. On dit le nombre.
+narrateur|Nina touche une cuillère.
+enfant-f|Une.
+narrateur|Elle en touche une autre.
+enfant-f|Deux.
+enfant-f|Trois.
+enfant-f|Quatre.
+enfant-f|Cinq.
+papa|Cinq cuillères.
+maman|Tu as dit le nombre.
+narrateur|Maman en pose encore.
+narrateur|Le bois tape tout doux.
+enfant-f|Six.
+enfant-f|Sept.
+enfant-f|Huit.
+enfant-f|Neuf.
+enfant-f|Dix.
+papa|Dix.
+maman|Tu as compté des objets.
+enfant-f|Dix cuillères.
+papa|Bravo, Nina.
+papa|Tu as fait du bon travail.
+narrateur|Nina aligne les cuillères.
+narrateur|Les manches se touchent.
+maman|Les objets sont là.
+papa|On peut dire le nombre.
+narrateur|La soupe chuchote encore.
+narrateur|Le napperon reste beige.
+maman|Le bois est lisse, hein ?
+enfant-f|Oui. Lisse.
+papa|On range le tiroir ?
+enfant-f|Oui, papa.
+narrateur|Nina pose les cuillères une à une.
+narrateur|Le tiroir se ferme tout doux.
+narrateur|Papa pose des bols sur le napperon.
+narrateur|Les bols sont blancs et chauds.
+maman|On compte aussi les bols.
+narrateur|Nina touche un bol.
+enfant-f|Un. Deux. Trois. Quatre. Cinq.
+papa|Cinq bols.
+maman|Tu dis le nombre.
+enfant-f|Cinq.
+papa|Tu as compté des objets.
+narrateur|La vapeur sent encore la carotte.
+narrateur|Le carré de lumière a bougé.
+maman|Cuillères, puis bols.
+enfant-f|J'ai dit le nombre.
+papa|Le tiroir reste fermé.
+narrateur|Nina pose sa main sur le bois.
+narrateur|Le bois est tiède.</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1340,7 +1414,7 @@
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>Aurore touche les cuillères. Que fait-elle ?</t>
+          <t>Nina touche les cuillères. Que fait-elle ?</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
@@ -1496,10 +1570,10 @@
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>narrateur|Aurore touche les cuillères. Que fait-elle ?</t>
-        </is>
-      </c>
-      <c r="AX3" t="inlineStr"/>
+          <t>narrateur|Nina touche les cuillères.
+narrateur|Que fait-elle ?</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1524,7 +1598,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Aurore a compté des objets. Elle a dit le nombre.</t>
+          <t>Nina a compté des objets. Elle a dit le nombre. Tu as compté les cuillères ? Oui, maman. Bravo, Nina. Tu as fait du bon travail. Les cuillères reposent dans le tiroir. Le bois sent encore le chaud. Le tiroir est fermé ? Oui, maman. Une cuillère dépasse encore un peu.</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -1664,10 +1738,19 @@
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>narrateur|Aurore a compté des objets. Elle a dit le nombre.</t>
-        </is>
-      </c>
-      <c r="AX4" t="inlineStr"/>
+          <t>narrateur|Nina a compté des objets.
+narrateur|Elle a dit le nombre.
+maman|Tu as compté les cuillères ?
+enfant-f|Oui, maman.
+papa|Bravo, Nina.
+papa|Tu as fait du bon travail.
+narrateur|Les cuillères reposent dans le tiroir.
+narrateur|Le bois sent encore le chaud.
+maman|Le tiroir est fermé ?
+enfant-f|Oui, maman.
+narrateur|Une cuillère dépasse encore un peu.</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1692,7 +1775,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>Maman range les cuillères. Aurore essuie la table.</t>
+          <t>Nina pousse la cuillère. Je te sers un peu de soupe ? Oui, maman. Maman verse tout doux. La vapeur sent la carotte. Tu as fini de compter ? Oui, papa. Bravo. Le napperon reste sur la table. On goûte ? Oui. Ça sent bon, tout près.</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -1828,10 +1911,20 @@
       <c r="AV5" s="2" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>narrateur|Maman range les cuillères. Aurore essuie la table.</t>
-        </is>
-      </c>
-      <c r="AX5" t="inlineStr"/>
+          <t>narrateur|Nina pousse la cuillère.
+maman|Je te sers un peu de soupe ?
+enfant-f|Oui, maman.
+narrateur|Maman verse tout doux.
+narrateur|La vapeur sent la carotte.
+papa|Tu as fini de compter ?
+enfant-f|Oui, papa.
+papa|Bravo.
+narrateur|Le napperon reste sur la table.
+maman|On goûte ?
+enfant-f|Oui.
+narrateur|Ça sent bon, tout près.</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -1856,7 +1949,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Nina tient sa cuillère des deux mains. La soupe sent les carottes. Merci d'avoir compté. On touche. On dit le nombre. Oui. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -1996,10 +2089,14 @@
       <c r="AV6" s="2" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
-        </is>
-      </c>
-      <c r="AX6" t="inlineStr"/>
+          <t>narrateur|Nina tient sa cuillère des deux mains.
+narrateur|La soupe sent les carottes.
+maman|Merci d'avoir compté.
+papa|On touche. On dit le nombre.
+enfant-f|Oui.
+narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -2018,7 +2115,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A5"/>
+  <dimension ref="A1:A6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2056,6 +2153,13 @@
       <c r="A5" t="inlineStr">
         <is>
           <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>F-NAR-009 ouverture du monde, fusion agents</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-LAN.NOM.001-06.xlsx
+++ b/stories/arbres/ATOM-LAN.NOM.001-06.xlsx
@@ -544,7 +544,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Nina compte les cuillères</t>
+          <t>Les cuillères de Chouchou</t>
         </is>
       </c>
     </row>
@@ -841,7 +841,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Le tiroir grince. Nina touche les cuillères de bois. Elle compte jusqu'à dix. Papa et maman disent le nombre.</t>
+          <t>La vapeur de la soupe embue. Chouchou touche les cuillères sur la nappe. Cinq, puis dix. Il dit le nombre.</t>
         </is>
       </c>
     </row>
@@ -1184,12 +1184,12 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Le tiroir grince, puis s'ouvre. Le bois sent le chaud de la pièce. Une cuillère en bois dépasse. Le manche est lisse et un peu taché. La casserole chuchote sur le feu doux. Ça sent la soupe de carottes. Un napperon beige attend sur la table. Il a un petit trou au coin. La fenêtre laisse un carré de lumière. Nina, tu as entendu le tiroir ? Oui, papa. Ça grince. Les cuillères sont là. Ça sent la soupe. En ce moment, Nina s'approche de la table. Des cuillères sont alignées. Elles sont en bois, un peu mates. On compte des objets. On touche. On dit le nombre. Nina touche une cuillère. Une. Elle en touche une autre. Deux. Trois. Quatre. Cinq. Cinq cuillères. Tu as dit le nombre. Maman en pose encore. Le bois tape tout doux. Six. Sept. Huit. Neuf. Dix. Dix. Tu as compté des objets. Dix cuillères. Bravo, Nina. Tu as fait du bon travail. Nina aligne les cuillères. Les manches se touchent. Les objets sont là. On peut dire le nombre. La soupe chuchote encore. Le napperon reste beige. Le bois est lisse, hein ? Oui. Lisse. On range le tiroir ? Oui, papa. Nina pose les cuillères une à une. Le tiroir se ferme tout doux. Papa pose des bols sur le napperon. Les bols sont blancs et chauds. On compte aussi les bols. Nina touche un bol. Un. Deux. Trois. Quatre. Cinq. Cinq bols. Tu dis le nombre. Cinq. Tu as compté des objets. La vapeur sent encore la carotte. Le carré de lumière a bougé. Cuillères, puis bols. J'ai dit le nombre. Le tiroir reste fermé. Nina pose sa main sur le bois. Le bois est tiède.</t>
+          <t>La vapeur de la soupe embue la casserole. Ça sent le potiron, tout doux. La nappe à carreaux est un peu froissée. Le tiroir de bois est ouvert. Les cuillères font un petit bruit. Une miette de pain attend près de l'assiette. La fenêtre a un coin embué. Tu as senti la soupe, Chouchou ? Oui, maman. Ça sent le potiron. On met la table, tout doux. En ce moment, Chouchou s'approche de la table. Des cuillères sont sur la nappe. Elles brillent un peu. On va compter des objets. Des cuillères. Des cuillères. Chouchou touche une cuillère. Elle est lisse et un peu froide. Une. Une. Il en touche une autre. Deux. Trois. Quatre. Cinq. Cinq cuillères. Tu as dit le nombre. Cinq. Maman en pose encore. On continue. Six. Sept. Huit. Neuf. Dix. Dix. Tu as dit le nombre. Dix. Bravo, Chouchou. Tu as compté des objets. C'est du bon travail. Les cuillères restent en ligne. On les pose une à une ? Oui, maman. Chouchou pose les cuillères. Une, deux, trois, quatre, cinq. Six, sept, huit, neuf, dix. Les objets sont là. Tu les as comptés. Dix cuillères. Oui. Cinq, puis dix. La vapeur a un peu reculé. La nappe sent encore le pain. Tu as fini de compter ? Oui. Dix. Bravo. Tu as compté des objets. Une goutte de vapeur glisse. Elle fait un petit trait sur le couvercle. La nappe est douce. Oui. À carreaux. Le tiroir de bois attend encore. Une cuillère pour papa. Une cuillère pour maman. Et une pour moi. Oui. Les autres attendent. Tu as compté des objets. Dix cuillères. Tu as dit le nombre. La soupe sent encore le potiron.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Aurore est à la cuisine avec maman. Des cuillères sont sur la table. Maman dit : on compte des objets. Aurore touche. Un. Deux. Trois. Quatre. Cinq. Elle dit : cinq cuillères. Maman en pose encore. Six. Sept. Huit. Neuf. Dix. Aurore répète : dix. Elle a compté des objets. Elle a dit le nombre.&lt;/prosody&gt;&lt;break time="400ms"/&gt;&lt;/speak&gt;</t>
+          <t>La vapeur de la soupe embue la casserole. Ça sent le potiron, tout doux. La nappe à carreaux est un peu froissée. Le tiroir de bois est ouvert. Les cuillères font un petit bruit. Une miette de pain attend près de l'assiette. La fenêtre a un coin embué. Tu as senti la soupe, Chouchou ? Oui, maman. Ça sent le potiron. On met la table, tout doux. En ce moment, Chouchou s'approche de la table. Des cuillères sont sur la nappe. Elles brillent un peu. On va compter des objets. Des cuillères. Des cuillères. Chouchou touche une cuillère. Elle est lisse et un peu froide. Une. Une. Il en touche une autre. Deux. Trois. Quatre. Cinq. Cinq cuillères. Tu as dit le nombre. Cinq. Maman en pose encore. On continue. Six. Sept. Huit. Neuf. Dix. Dix. Tu as dit le nombre. Dix. Bravo, Chouchou. Tu as compté des objets. C'est du bon travail. Les cuillères restent en ligne. On les pose une à une ? Oui, maman. Chouchou pose les cuillères. Une, deux, trois, quatre, cinq. Six, sept, huit, neuf, dix. Les objets sont là. Tu les as comptés. Dix cuillères. Oui. Cinq, puis dix. La vapeur a un peu reculé. La nappe sent encore le pain. Tu as fini de compter ? Oui. Dix. Bravo. Tu as compté des objets. Une goutte de vapeur glisse. Elle fait un petit trait sur le couvercle. La nappe est douce. Oui. À carreaux. Le tiroir de bois attend encore. Une cuillère pour papa. Une cuillère pour maman. Et une pour moi. Oui. Les autres attendent. Tu as compté des objets. Dix cuillères. Tu as dit le nombre. La soupe sent encore le potiron.</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
@@ -1320,74 +1320,81 @@
       <c r="AV2" s="2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>narrateur|Le tiroir grince, puis s'ouvre.
-narrateur|Le bois sent le chaud de la pièce.
-narrateur|Une cuillère en bois dépasse.
-narrateur|Le manche est lisse et un peu taché.
-narrateur|La casserole chuchote sur le feu doux.
-narrateur|Ça sent la soupe de carottes.
-narrateur|Un napperon beige attend sur la table.
-narrateur|Il a un petit trou au coin.
-narrateur|La fenêtre laisse un carré de lumière.
-papa|Nina, tu as entendu le tiroir ?
-enfant-f|Oui, papa.
-enfant-f|Ça grince.
-maman|Les cuillères sont là.
-papa|Ça sent la soupe.
-narrateur|En ce moment, Nina s'approche de la table.
-narrateur|Des cuillères sont alignées.
-narrateur|Elles sont en bois, un peu mates.
-maman|On compte des objets.
-papa|On touche. On dit le nombre.
-narrateur|Nina touche une cuillère.
-enfant-f|Une.
-narrateur|Elle en touche une autre.
-enfant-f|Deux.
-enfant-f|Trois.
-enfant-f|Quatre.
-enfant-f|Cinq.
-papa|Cinq cuillères.
+          <t>narrateur|La vapeur de la soupe embue la casserole.
+narrateur|Ça sent le potiron, tout doux.
+narrateur|La nappe à carreaux est un peu froissée.
+narrateur|Le tiroir de bois est ouvert.
+narrateur|Les cuillères font un petit bruit.
+narrateur|Une miette de pain attend près de l'assiette.
+narrateur|La fenêtre a un coin embué.
+maman|Tu as senti la soupe, Chouchou ?
+enfant-m|Oui, maman.
+enfant-m|Ça sent le potiron.
+maman|On met la table, tout doux.
+narrateur|En ce moment, Chouchou s'approche de la table.
+narrateur|Des cuillères sont sur la nappe.
+narrateur|Elles brillent un peu.
+maman|On va compter des objets.
+maman|Des cuillères.
+enfant-m|Des cuillères.
+narrateur|Chouchou touche une cuillère.
+narrateur|Elle est lisse et un peu froide.
+maman|Une.
+enfant-m|Une.
+narrateur|Il en touche une autre.
+enfant-m|Deux.
+enfant-m|Trois.
+enfant-m|Quatre.
+enfant-m|Cinq.
+enfant-m|Cinq cuillères.
 maman|Tu as dit le nombre.
+maman|Cinq.
 narrateur|Maman en pose encore.
-narrateur|Le bois tape tout doux.
-enfant-f|Six.
-enfant-f|Sept.
-enfant-f|Huit.
-enfant-f|Neuf.
-enfant-f|Dix.
-papa|Dix.
+maman|On continue.
+enfant-m|Six.
+enfant-m|Sept.
+enfant-m|Huit.
+enfant-m|Neuf.
+enfant-m|Dix.
+enfant-m|Dix.
+maman|Tu as dit le nombre.
+maman|Dix.
+maman|Bravo, Chouchou.
 maman|Tu as compté des objets.
-enfant-f|Dix cuillères.
-papa|Bravo, Nina.
-papa|Tu as fait du bon travail.
-narrateur|Nina aligne les cuillères.
-narrateur|Les manches se touchent.
+maman|C'est du bon travail.
+narrateur|Les cuillères restent en ligne.
+maman|On les pose une à une ?
+enfant-m|Oui, maman.
+narrateur|Chouchou pose les cuillères.
+enfant-m|Une, deux, trois, quatre, cinq.
+enfant-m|Six, sept, huit, neuf, dix.
 maman|Les objets sont là.
-papa|On peut dire le nombre.
-narrateur|La soupe chuchote encore.
-narrateur|Le napperon reste beige.
-maman|Le bois est lisse, hein ?
-enfant-f|Oui. Lisse.
-papa|On range le tiroir ?
-enfant-f|Oui, papa.
-narrateur|Nina pose les cuillères une à une.
-narrateur|Le tiroir se ferme tout doux.
-narrateur|Papa pose des bols sur le napperon.
-narrateur|Les bols sont blancs et chauds.
-maman|On compte aussi les bols.
-narrateur|Nina touche un bol.
-enfant-f|Un. Deux. Trois. Quatre. Cinq.
-papa|Cinq bols.
-maman|Tu dis le nombre.
-enfant-f|Cinq.
-papa|Tu as compté des objets.
-narrateur|La vapeur sent encore la carotte.
-narrateur|Le carré de lumière a bougé.
-maman|Cuillères, puis bols.
-enfant-f|J'ai dit le nombre.
-papa|Le tiroir reste fermé.
-narrateur|Nina pose sa main sur le bois.
-narrateur|Le bois est tiède.</t>
+maman|Tu les as comptés.
+enfant-m|Dix cuillères.
+maman|Oui.
+maman|Cinq, puis dix.
+narrateur|La vapeur a un peu reculé.
+narrateur|La nappe sent encore le pain.
+maman|Tu as fini de compter ?
+enfant-m|Oui.
+enfant-m|Dix.
+maman|Bravo.
+maman|Tu as compté des objets.
+narrateur|Une goutte de vapeur glisse.
+narrateur|Elle fait un petit trait sur le couvercle.
+enfant-m|La nappe est douce.
+maman|Oui.
+maman|À carreaux.
+narrateur|Le tiroir de bois attend encore.
+maman|Une cuillère pour papa.
+maman|Une cuillère pour maman.
+enfant-m|Et une pour moi.
+maman|Oui.
+maman|Les autres attendent.
+maman|Tu as compté des objets.
+enfant-m|Dix cuillères.
+maman|Tu as dit le nombre.
+narrateur|La soupe sent encore le potiron.</t>
         </is>
       </c>
     </row>
@@ -1414,12 +1421,12 @@
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>Nina touche les cuillères. Que fait-elle ?</t>
+          <t>Chouchou touche les cuillères. Que fait-il ?</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Aurore touche les cuillères. Que fait-elle ?&lt;/prosody&gt;&lt;break time="250ms"/&gt;&lt;/speak&gt;</t>
+          <t>Chouchou touche les cuillères. Que fait-il ?</t>
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr">
@@ -1570,8 +1577,8 @@
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>narrateur|Nina touche les cuillères.
-narrateur|Que fait-elle ?</t>
+          <t>narrateur|Chouchou touche les cuillères.
+narrateur|Que fait-il ?</t>
         </is>
       </c>
     </row>
@@ -1598,12 +1605,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Nina a compté des objets. Elle a dit le nombre. Tu as compté les cuillères ? Oui, maman. Bravo, Nina. Tu as fait du bon travail. Les cuillères reposent dans le tiroir. Le bois sent encore le chaud. Le tiroir est fermé ? Oui, maman. Une cuillère dépasse encore un peu.</t>
+          <t>Chouchou a compté des objets. Il a dit le nombre. Dix cuillères. Bravo, Chouchou. Dix. Tu as fait du bon travail. Les cuillères restent sur la nappe. La soupe chante encore, tout doux.</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Aurore a compté des objets. Elle a dit le nombre.&lt;/prosody&gt;&lt;break time="450ms"/&gt;&lt;/speak&gt;</t>
+          <t>Chouchou a compté des objets. Il a dit le nombre. Dix cuillères. Bravo, Chouchou. Dix. Tu as fait du bon travail. Les cuillères restent sur la nappe. La soupe chante encore, tout doux.</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -1738,17 +1745,14 @@
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>narrateur|Nina a compté des objets.
-narrateur|Elle a dit le nombre.
-maman|Tu as compté les cuillères ?
-enfant-f|Oui, maman.
-papa|Bravo, Nina.
-papa|Tu as fait du bon travail.
-narrateur|Les cuillères reposent dans le tiroir.
-narrateur|Le bois sent encore le chaud.
-maman|Le tiroir est fermé ?
-enfant-f|Oui, maman.
-narrateur|Une cuillère dépasse encore un peu.</t>
+          <t>narrateur|Chouchou a compté des objets.
+narrateur|Il a dit le nombre.
+maman|Dix cuillères.
+maman|Bravo, Chouchou.
+enfant-m|Dix.
+maman|Tu as fait du bon travail.
+narrateur|Les cuillères restent sur la nappe.
+narrateur|La soupe chante encore, tout doux.</t>
         </is>
       </c>
     </row>
@@ -1775,12 +1779,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>Nina pousse la cuillère. Je te sers un peu de soupe ? Oui, maman. Maman verse tout doux. La vapeur sent la carotte. Tu as fini de compter ? Oui, papa. Bravo. Le napperon reste sur la table. On goûte ? Oui. Ça sent bon, tout près.</t>
+          <t>On range les cuillères ? Oui, maman. Maman range les cuillères. Chouchou essuie la table. Tu as fini d'essuyer ? Oui, maman. Bravo. La miette de pain n'est plus là. Le tiroir de bois se ferme. Ça sent encore le potiron. On attend la soupe un moment ? Oui, maman. Ils s'assoient. La nappe est douce sous les mains. Tu as bien compté. Cinq, puis dix. Une cuillère reste près de l'assiette. Elle brille un peu.</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Maman range les cuillères. Aurore essuie la table.&lt;/prosody&gt;&lt;break time="450ms"/&gt;&lt;/speak&gt;</t>
+          <t>On range les cuillères ? Oui, maman. Maman range les cuillères. Chouchou essuie la table. Tu as fini d'essuyer ? Oui, maman. Bravo. La miette de pain n'est plus là. Le tiroir de bois se ferme. Ça sent encore le potiron. On attend la soupe un moment ? Oui, maman. Ils s'assoient. La nappe est douce sous les mains. Tu as bien compté. Cinq, puis dix. Une cuillère reste près de l'assiette. Elle brille un peu.</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -1911,18 +1915,24 @@
       <c r="AV5" s="2" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>narrateur|Nina pousse la cuillère.
-maman|Je te sers un peu de soupe ?
-enfant-f|Oui, maman.
-narrateur|Maman verse tout doux.
-narrateur|La vapeur sent la carotte.
-papa|Tu as fini de compter ?
-enfant-f|Oui, papa.
-papa|Bravo.
-narrateur|Le napperon reste sur la table.
-maman|On goûte ?
-enfant-f|Oui.
-narrateur|Ça sent bon, tout près.</t>
+          <t>maman|On range les cuillères ?
+enfant-m|Oui, maman.
+narrateur|Maman range les cuillères.
+narrateur|Chouchou essuie la table.
+maman|Tu as fini d'essuyer ?
+enfant-m|Oui, maman.
+maman|Bravo.
+narrateur|La miette de pain n'est plus là.
+narrateur|Le tiroir de bois se ferme.
+narrateur|Ça sent encore le potiron.
+maman|On attend la soupe un moment ?
+enfant-m|Oui, maman.
+narrateur|Ils s'assoient.
+narrateur|La nappe est douce sous les mains.
+maman|Tu as bien compté.
+enfant-m|Cinq, puis dix.
+narrateur|Une cuillère reste près de l'assiette.
+narrateur|Elle brille un peu.</t>
         </is>
       </c>
     </row>
@@ -1949,12 +1959,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>Nina tient sa cuillère des deux mains. La soupe sent les carottes. Merci d'avoir compté. On touche. On dit le nombre. Oui. L'histoire est finie.</t>
+          <t>La casserole n'embue plus. Dix cuillères. Tu as compté des objets. Bravo, Chouchou. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="low"&gt;L'histoire est finie.&lt;/prosody&gt;&lt;break time="600ms"/&gt;&lt;/speak&gt;</t>
+          <t>La casserole n'embue plus. Dix cuillères. Tu as compté des objets. Bravo, Chouchou. L'histoire est finie.</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -2089,11 +2099,10 @@
       <c r="AV6" s="2" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>narrateur|Nina tient sa cuillère des deux mains.
-narrateur|La soupe sent les carottes.
-maman|Merci d'avoir compté.
-papa|On touche. On dit le nombre.
-enfant-f|Oui.
+          <t>narrateur|La casserole n'embue plus.
+enfant-m|Dix cuillères.
+maman|Tu as compté des objets.
+maman|Bravo, Chouchou.
 narrateur|L'histoire est finie.</t>
         </is>
       </c>
@@ -2115,7 +2124,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A6"/>
+  <dimension ref="A1:A7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2160,6 +2169,13 @@
       <c r="A6" t="inlineStr">
         <is>
           <t>F-NAR-009 ouverture du monde, fusion agents</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>F-NAR-008 récit, pas une leçon en puces</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-LAN.NOM.001-06.xlsx
+++ b/stories/arbres/ATOM-LAN.NOM.001-06.xlsx
@@ -1184,12 +1184,12 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>La vapeur de la soupe embue la casserole. Ça sent le potiron, tout doux. La nappe à carreaux est un peu froissée. Le tiroir de bois est ouvert. Les cuillères font un petit bruit. Une miette de pain attend près de l'assiette. La fenêtre a un coin embué. Tu as senti la soupe, Chouchou ? Oui, maman. Ça sent le potiron. On met la table, tout doux. En ce moment, Chouchou s'approche de la table. Des cuillères sont sur la nappe. Elles brillent un peu. On va compter des objets. Des cuillères. Des cuillères. Chouchou touche une cuillère. Elle est lisse et un peu froide. Une. Une. Il en touche une autre. Deux. Trois. Quatre. Cinq. Cinq cuillères. Tu as dit le nombre. Cinq. Maman en pose encore. On continue. Six. Sept. Huit. Neuf. Dix. Dix. Tu as dit le nombre. Dix. Bravo, Chouchou. Tu as compté des objets. C'est du bon travail. Les cuillères restent en ligne. On les pose une à une ? Oui, maman. Chouchou pose les cuillères. Une, deux, trois, quatre, cinq. Six, sept, huit, neuf, dix. Les objets sont là. Tu les as comptés. Dix cuillères. Oui. Cinq, puis dix. La vapeur a un peu reculé. La nappe sent encore le pain. Tu as fini de compter ? Oui. Dix. Bravo. Tu as compté des objets. Une goutte de vapeur glisse. Elle fait un petit trait sur le couvercle. La nappe est douce. Oui. À carreaux. Le tiroir de bois attend encore. Une cuillère pour papa. Une cuillère pour maman. Et une pour moi. Oui. Les autres attendent. Tu as compté des objets. Dix cuillères. Tu as dit le nombre. La soupe sent encore le potiron.</t>
+          <t>La vapeur de la soupe embue la casserole. Ça sent le potiron, tout doux. La nappe à carreaux est un peu froissée. Le tiroir de bois est ouvert. Les cuillères font un petit bruit. Une miette de pain attend près de l'assiette. La fenêtre a un coin embué. Tu as senti la soupe, Chouchou ? Oui, maman. Ça sent le potiron. On met la table, tout doux. En ce moment, Chouchou s'approche de la table. Des cuillères sont sur la nappe. Elles brillent un peu. On va compter des objets. Des cuillères. Des cuillères. Chouchou touche une cuillère. Elle est lisse et un peu froide. Une. Une. Il en touche une autre. Deux. Trois. Quatre. Cinq. Cinq cuillères. Tu as dit le nombre. Cinq. Maman en pose encore. On continue. Six. Sept. Huit. Neuf. Dix. Dix. Tu as dit le nombre. Dix. Bravo, Chouchou. Tu as compté des objets. Les cuillères restent en ligne. On les pose une à une ? Oui, maman. Chouchou pose les cuillères. Une, deux, trois, quatre, cinq. Six, sept, huit, neuf, dix. Les objets sont là. Tu les as comptés. Dix cuillères. Oui. Cinq, puis dix. La vapeur a un peu reculé. La nappe sent encore le pain. Tu as fini de compter ? Oui. Dix. Bravo. Tu as compté des objets. Une goutte de vapeur glisse. Elle fait un petit trait sur le couvercle. La nappe est douce. Oui. À carreaux. Le tiroir de bois attend encore. Une cuillère pour papa. Une cuillère pour maman. Et une pour moi. Oui. Les autres attendent. Tu as compté des objets. Dix cuillères. Tu as dit le nombre. La soupe sent encore le potiron.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>La vapeur de la soupe embue la casserole. Ça sent le potiron, tout doux. La nappe à carreaux est un peu froissée. Le tiroir de bois est ouvert. Les cuillères font un petit bruit. Une miette de pain attend près de l'assiette. La fenêtre a un coin embué. Tu as senti la soupe, Chouchou ? Oui, maman. Ça sent le potiron. On met la table, tout doux. En ce moment, Chouchou s'approche de la table. Des cuillères sont sur la nappe. Elles brillent un peu. On va compter des objets. Des cuillères. Des cuillères. Chouchou touche une cuillère. Elle est lisse et un peu froide. Une. Une. Il en touche une autre. Deux. Trois. Quatre. Cinq. Cinq cuillères. Tu as dit le nombre. Cinq. Maman en pose encore. On continue. Six. Sept. Huit. Neuf. Dix. Dix. Tu as dit le nombre. Dix. Bravo, Chouchou. Tu as compté des objets. C'est du bon travail. Les cuillères restent en ligne. On les pose une à une ? Oui, maman. Chouchou pose les cuillères. Une, deux, trois, quatre, cinq. Six, sept, huit, neuf, dix. Les objets sont là. Tu les as comptés. Dix cuillères. Oui. Cinq, puis dix. La vapeur a un peu reculé. La nappe sent encore le pain. Tu as fini de compter ? Oui. Dix. Bravo. Tu as compté des objets. Une goutte de vapeur glisse. Elle fait un petit trait sur le couvercle. La nappe est douce. Oui. À carreaux. Le tiroir de bois attend encore. Une cuillère pour papa. Une cuillère pour maman. Et une pour moi. Oui. Les autres attendent. Tu as compté des objets. Dix cuillères. Tu as dit le nombre. La soupe sent encore le potiron.</t>
+          <t>La vapeur de la soupe embue la casserole. Ça sent le potiron, tout doux. La nappe à carreaux est un peu froissée. Le tiroir de bois est ouvert. Les cuillères font un petit bruit. Une miette de pain attend près de l'assiette. La fenêtre a un coin embué. Tu as senti la soupe, Chouchou ? Oui, maman. Ça sent le potiron. On met la table, tout doux. En ce moment, Chouchou s'approche de la table. Des cuillères sont sur la nappe. Elles brillent un peu. On va compter des objets. Des cuillères. Des cuillères. Chouchou touche une cuillère. Elle est lisse et un peu froide. Une. Une. Il en touche une autre. Deux. Trois. Quatre. Cinq. Cinq cuillères. Tu as dit le nombre. Cinq. Maman en pose encore. On continue. Six. Sept. Huit. Neuf. Dix. Dix. Tu as dit le nombre. Dix. Bravo, Chouchou. Tu as compté des objets. Les cuillères restent en ligne. On les pose une à une ? Oui, maman. Chouchou pose les cuillères. Une, deux, trois, quatre, cinq. Six, sept, huit, neuf, dix. Les objets sont là. Tu les as comptés. Dix cuillères. Oui. Cinq, puis dix. La vapeur a un peu reculé. La nappe sent encore le pain. Tu as fini de compter ? Oui. Dix. Bravo. Tu as compté des objets. Une goutte de vapeur glisse. Elle fait un petit trait sur le couvercle. La nappe est douce. Oui. À carreaux. Le tiroir de bois attend encore. Une cuillère pour papa. Une cuillère pour maman. Et une pour moi. Oui. Les autres attendent. Tu as compté des objets. Dix cuillères. Tu as dit le nombre. La soupe sent encore le potiron.</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
@@ -1361,7 +1361,6 @@
 maman|Dix.
 maman|Bravo, Chouchou.
 maman|Tu as compté des objets.
-maman|C'est du bon travail.
 narrateur|Les cuillères restent en ligne.
 maman|On les pose une à une ?
 enfant-m|Oui, maman.
@@ -1605,12 +1604,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Chouchou a compté des objets. Il a dit le nombre. Dix cuillères. Bravo, Chouchou. Dix. Tu as fait du bon travail. Les cuillères restent sur la nappe. La soupe chante encore, tout doux.</t>
+          <t>Chouchou a compté des objets. Il a dit le nombre. Dix cuillères. Bravo, Chouchou. Dix. Les cuillères restent sur la nappe. La soupe chante encore, tout doux.</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>Chouchou a compté des objets. Il a dit le nombre. Dix cuillères. Bravo, Chouchou. Dix. Tu as fait du bon travail. Les cuillères restent sur la nappe. La soupe chante encore, tout doux.</t>
+          <t>Chouchou a compté des objets. Il a dit le nombre. Dix cuillères. Bravo, Chouchou. Dix. Les cuillères restent sur la nappe. La soupe chante encore, tout doux.</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -1750,7 +1749,6 @@
 maman|Dix cuillères.
 maman|Bravo, Chouchou.
 enfant-m|Dix.
-maman|Tu as fait du bon travail.
 narrateur|Les cuillères restent sur la nappe.
 narrateur|La soupe chante encore, tout doux.</t>
         </is>
@@ -1959,12 +1957,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>La casserole n'embue plus. Dix cuillères. Tu as compté des objets. Bravo, Chouchou. L'histoire est finie.</t>
+          <t>La casserole n'embue plus. Dix cuillères. Tu as compté des objets. Bravo, Chouchou.</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>La casserole n'embue plus. Dix cuillères. Tu as compté des objets. Bravo, Chouchou. L'histoire est finie.</t>
+          <t>La casserole n'embue plus. Dix cuillères. Tu as compté des objets. Bravo, Chouchou.</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -2102,8 +2100,7 @@
           <t>narrateur|La casserole n'embue plus.
 enfant-m|Dix cuillères.
 maman|Tu as compté des objets.
-maman|Bravo, Chouchou.
-narrateur|L'histoire est finie.</t>
+maman|Bravo, Chouchou.</t>
         </is>
       </c>
     </row>
@@ -2124,7 +2121,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A7"/>
+  <dimension ref="A1:A8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2174,6 +2171,13 @@
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
+        <is>
+          <t>F-NAR-008 récit, pas une leçon en puces</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
         <is>
           <t>F-NAR-008 récit, pas une leçon en puces</t>
         </is>

--- a/stories/arbres/ATOM-LAN.NOM.001-06.xlsx
+++ b/stories/arbres/ATOM-LAN.NOM.001-06.xlsx
@@ -671,7 +671,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>cuisine</t>
+          <t>cuisine, avant le repas</t>
         </is>
       </c>
     </row>
@@ -683,7 +683,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Aurore, maman</t>
+          <t>Chouchou, maman</t>
         </is>
       </c>
     </row>
